--- a/data/fall2425_ra_info.xlsx
+++ b/data/fall2425_ra_info.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\berkercin\Desktop\Projects\Scheduling\Campus-Scheduling\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C716D8DF-D1C8-4A60-BA32-CB35BC5D7CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE976BD-C853-41D1-99D9-495BC3664A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arş.Gör." sheetId="5" r:id="rId1"/>
@@ -955,30 +955,51 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,27 +1020,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1300,15 +1300,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF40D47-426B-49AC-A8EF-9525ED7418DB}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="70" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="16">
@@ -1320,8 +1320,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64"/>
+    <row r="2" spans="1:3" s="12" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="77"/>
       <c r="B2" s="14" t="s">
         <v>63</v>
       </c>
@@ -1329,343 +1329,343 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63" t="s">
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
-    </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+    </row>
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="67">
+      <c r="B4" s="75">
         <v>8</v>
       </c>
-      <c r="C4" s="65">
+      <c r="C4" s="73">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="65"/>
-    </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="75"/>
+      <c r="C5" s="73"/>
+    </row>
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="65"/>
-    </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="75"/>
+      <c r="C6" s="73"/>
+    </row>
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="65"/>
-    </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="75"/>
+      <c r="C7" s="73"/>
+    </row>
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-    </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="75"/>
+      <c r="C8" s="73"/>
+    </row>
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="65"/>
-    </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="75"/>
+      <c r="C9" s="73"/>
+    </row>
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="67"/>
-      <c r="C10" s="65"/>
-    </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="75"/>
+      <c r="C10" s="73"/>
+    </row>
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="65"/>
-    </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="75"/>
+      <c r="C11" s="73"/>
+    </row>
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="66"/>
-    </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63" t="s">
+      <c r="B12" s="76"/>
+      <c r="C12" s="74"/>
+    </row>
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="70"/>
-    </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="71"/>
+      <c r="C13" s="72"/>
+    </row>
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="67">
+      <c r="B14" s="75">
         <v>1</v>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="73">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="66"/>
-    </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="63" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="74"/>
+    </row>
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-    </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="71"/>
+      <c r="C16" s="72"/>
+    </row>
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="67">
+      <c r="B17" s="75">
         <v>5</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="73">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="65"/>
-    </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="75"/>
+      <c r="C18" s="73"/>
+    </row>
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="65"/>
-    </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="75"/>
+      <c r="C19" s="73"/>
+    </row>
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="65"/>
-    </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="75"/>
+      <c r="C20" s="73"/>
+    </row>
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="65"/>
-    </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="75"/>
+      <c r="C21" s="73"/>
+    </row>
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="67"/>
-      <c r="C22" s="65"/>
-    </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="75"/>
+      <c r="C22" s="73"/>
+    </row>
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="66"/>
-    </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63" t="s">
+      <c r="B23" s="76"/>
+      <c r="C23" s="74"/>
+    </row>
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="69"/>
-      <c r="C24" s="70"/>
-    </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="71"/>
+      <c r="C24" s="72"/>
+    </row>
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="67">
+      <c r="B25" s="75">
         <v>4</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="73">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="65"/>
-    </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="75"/>
+      <c r="C26" s="73"/>
+    </row>
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="67"/>
-      <c r="C27" s="65"/>
-    </row>
-    <row r="28" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="75"/>
+      <c r="C27" s="73"/>
+    </row>
+    <row r="28" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="68"/>
-      <c r="C28" s="66"/>
-    </row>
-    <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63" t="s">
+      <c r="B28" s="76"/>
+      <c r="C28" s="74"/>
+    </row>
+    <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="70"/>
-    </row>
-    <row r="30" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="71"/>
+      <c r="C29" s="72"/>
+    </row>
+    <row r="30" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="67">
+      <c r="B30" s="75">
         <v>4</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="73">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="65"/>
-    </row>
-    <row r="32" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="75"/>
+      <c r="C31" s="73"/>
+    </row>
+    <row r="32" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="67"/>
-      <c r="C32" s="65"/>
-    </row>
-    <row r="33" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="75"/>
+      <c r="C32" s="73"/>
+    </row>
+    <row r="33" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="65"/>
-    </row>
-    <row r="34" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="75"/>
+      <c r="C33" s="73"/>
+    </row>
+    <row r="34" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-    </row>
-    <row r="35" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="75"/>
+      <c r="C34" s="73"/>
+    </row>
+    <row r="35" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="68"/>
-      <c r="C35" s="66"/>
-    </row>
-    <row r="36" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="63" t="s">
+      <c r="B35" s="76"/>
+      <c r="C35" s="74"/>
+    </row>
+    <row r="36" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="70"/>
-    </row>
-    <row r="37" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="71"/>
+      <c r="C36" s="72"/>
+    </row>
+    <row r="37" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="67">
+      <c r="B37" s="75">
         <v>0</v>
       </c>
-      <c r="C37" s="65">
+      <c r="C37" s="73">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="67"/>
-      <c r="C38" s="65"/>
-    </row>
-    <row r="39" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="75"/>
+      <c r="C38" s="73"/>
+    </row>
+    <row r="39" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="67"/>
-      <c r="C39" s="65"/>
-    </row>
-    <row r="40" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="75"/>
+      <c r="C39" s="73"/>
+    </row>
+    <row r="40" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="68"/>
-      <c r="C40" s="66"/>
-    </row>
-    <row r="41" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="63" t="s">
+      <c r="B40" s="76"/>
+      <c r="C40" s="74"/>
+    </row>
+    <row r="41" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="69"/>
-      <c r="C41" s="70"/>
-    </row>
-    <row r="42" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="71"/>
+      <c r="C41" s="72"/>
+    </row>
+    <row r="42" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="67">
+      <c r="B42" s="75">
         <v>4</v>
       </c>
-      <c r="C42" s="65">
+      <c r="C42" s="73">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="67"/>
-      <c r="C43" s="65"/>
-    </row>
-    <row r="44" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="75"/>
+      <c r="C43" s="73"/>
+    </row>
+    <row r="44" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-    </row>
-    <row r="45" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="75"/>
+      <c r="C44" s="73"/>
+    </row>
+    <row r="45" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="68"/>
-      <c r="C45" s="66"/>
-    </row>
-    <row r="46" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="63" t="s">
+      <c r="B45" s="76"/>
+      <c r="C45" s="74"/>
+    </row>
+    <row r="46" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="69"/>
-      <c r="C46" s="70"/>
-    </row>
-    <row r="47" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="71"/>
+      <c r="C46" s="72"/>
+    </row>
+    <row r="47" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>53</v>
       </c>
@@ -1676,44 +1676,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="63" t="s">
+    <row r="48" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="69"/>
-      <c r="C48" s="70"/>
-    </row>
-    <row r="49" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="71"/>
+      <c r="C48" s="72"/>
+    </row>
+    <row r="49" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="67">
+      <c r="B49" s="75">
         <v>1</v>
       </c>
-      <c r="C49" s="65">
+      <c r="C49" s="73">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="68"/>
-      <c r="C50" s="66"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C17:C23"/>
-    <mergeCell ref="B17:B23"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="C30:C35"/>
-    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C4:C12"/>
+    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="B49:B50"/>
     <mergeCell ref="C42:C45"/>
     <mergeCell ref="B42:B45"/>
@@ -1723,12 +1718,17 @@
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C4:C12"/>
-    <mergeCell ref="B4:B12"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="C30:C35"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C17:C23"/>
+    <mergeCell ref="B17:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1740,17 +1740,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:O940"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="11.7109375" style="18" customWidth="1"/>
+    <col min="1" max="2" width="11.7265625" style="18" customWidth="1"/>
     <col min="3" max="3" width="34" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="17.140625" style="18" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="18" customWidth="1"/>
-    <col min="14" max="15" width="24.42578125" style="18" customWidth="1"/>
-    <col min="16" max="16384" width="14.42578125" style="18"/>
+    <col min="4" max="12" width="17.1796875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" style="18" customWidth="1"/>
+    <col min="14" max="15" width="24.453125" style="18" customWidth="1"/>
+    <col min="16" max="16384" width="14.453125" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17">
         <f>SUM(A3:A11)</f>
         <v>27</v>
@@ -1769,7 +1769,7 @@
       <c r="J1" s="17"/>
       <c r="K1" s="17"/>
     </row>
-    <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>63</v>
       </c>
@@ -1804,19 +1804,19 @@
         <v>71</v>
       </c>
       <c r="M2" s="1"/>
-      <c r="N2" s="72" t="s">
+      <c r="N2" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="O2" s="72"/>
-    </row>
-    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O2" s="79"/>
+    </row>
+    <row r="3" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
         <v>8</v>
       </c>
       <c r="B3" s="17">
         <v>0</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="63" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="58">
@@ -1857,18 +1857,18 @@
       <c r="N3" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="73" t="s">
+      <c r="O3" s="80" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
         <v>1</v>
       </c>
       <c r="B4" s="17">
         <v>1</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="66" t="s">
         <v>44</v>
       </c>
       <c r="D4" s="58">
@@ -1903,16 +1903,16 @@
       </c>
       <c r="M4" s="26"/>
       <c r="N4" s="62"/>
-      <c r="O4" s="73"/>
-    </row>
-    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="80"/>
+    </row>
+    <row r="5" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
         <v>6</v>
       </c>
       <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="64" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="58">
@@ -1953,16 +1953,16 @@
       <c r="N5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="73"/>
-    </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="80"/>
+    </row>
+    <row r="6" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
         <v>4</v>
       </c>
       <c r="B6" s="17">
         <v>0</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="67" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="58">
@@ -2003,16 +2003,16 @@
       <c r="N6" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="O6" s="73"/>
-    </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="80"/>
+    </row>
+    <row r="7" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17">
         <v>4</v>
       </c>
       <c r="B7" s="17">
         <v>2</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="68" t="s">
         <v>47</v>
       </c>
       <c r="D7" s="58">
@@ -2053,16 +2053,16 @@
       <c r="N7" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="73"/>
-    </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="80"/>
+    </row>
+    <row r="8" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17">
         <v>0</v>
       </c>
       <c r="B8" s="17">
         <v>3</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="65" t="s">
         <v>48</v>
       </c>
       <c r="D8" s="58">
@@ -2097,16 +2097,16 @@
       </c>
       <c r="M8" s="26"/>
       <c r="N8" s="25"/>
-      <c r="O8" s="73"/>
-    </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="80"/>
+    </row>
+    <row r="9" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17">
         <v>4</v>
       </c>
       <c r="B9" s="17">
         <v>0</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="69" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="58">
@@ -2141,9 +2141,9 @@
       </c>
       <c r="M9" s="26"/>
       <c r="N9" s="25"/>
-      <c r="O9" s="73"/>
-    </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="80"/>
+    </row>
+    <row r="10" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17">
         <v>0</v>
       </c>
@@ -2185,9 +2185,9 @@
       </c>
       <c r="M10" s="26"/>
       <c r="N10" s="25"/>
-      <c r="O10" s="73"/>
-    </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="80"/>
+    </row>
+    <row r="11" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17">
         <v>0</v>
       </c>
@@ -2229,9 +2229,9 @@
       </c>
       <c r="M11" s="26"/>
       <c r="N11" s="25"/>
-      <c r="O11" s="73"/>
-    </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="80"/>
+    </row>
+    <row r="12" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D12" s="58">
         <f t="shared" ref="D12:F12" si="5">SUM(D3:D11)</f>
         <v>507</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="K12" s="21"/>
     </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G13" s="42">
         <f>G12-F12</f>
         <v>515</v>
@@ -2281,11 +2281,11 @@
         <v>-3.2074324324324088</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
+    <row r="14" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="83"/>
       <c r="C14" s="29" t="s">
         <v>62</v>
       </c>
@@ -2297,11 +2297,11 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
+    <row r="15" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="77"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="30" t="s">
         <v>57</v>
       </c>
@@ -2328,11 +2328,11 @@
         <v>0.99377197585935462</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="77" t="s">
+    <row r="16" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="30" t="s">
         <v>79</v>
       </c>
@@ -2347,11 +2347,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="77" t="s">
+    <row r="17" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="77"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="30" t="s">
         <v>56</v>
       </c>
@@ -2367,11 +2367,11 @@
       </c>
       <c r="G17" s="21"/>
     </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="77" t="s">
+    <row r="18" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="77"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="30" t="s">
         <v>20</v>
       </c>
@@ -2386,11 +2386,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77" t="s">
+    <row r="19" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="77"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="30" t="s">
         <v>27</v>
       </c>
@@ -2405,11 +2405,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+    <row r="20" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="77"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="30" t="s">
         <v>26</v>
       </c>
@@ -2424,11 +2424,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="77" t="s">
+    <row r="21" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="77"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="30" t="s">
         <v>25</v>
       </c>
@@ -2443,11 +2443,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
+    <row r="22" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="84"/>
       <c r="C22" s="30" t="s">
         <v>53</v>
       </c>
@@ -2466,11 +2466,11 @@
         <v>450.77499999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
+    <row r="23" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="77"/>
+      <c r="B23" s="84"/>
       <c r="C23" s="30" t="s">
         <v>35</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2499,22 +2499,22 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="71" t="s">
+    <row r="25" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D26" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-    </row>
-    <row r="27" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="74" t="s">
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+    </row>
+    <row r="27" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="81" t="s">
         <v>81</v>
       </c>
       <c r="D27" s="51" t="s">
@@ -2545,8 +2545,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="75"/>
+    <row r="28" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C28" s="82"/>
       <c r="D28" s="22">
         <f>K3</f>
         <v>39.612612612612622</v>
@@ -2584,7 +2584,7 @@
         <v>7.9138888888888879</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C29" s="38" t="s">
         <v>72</v>
       </c>
@@ -2613,7 +2613,7 @@
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
     </row>
-    <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C30" s="51" t="s">
         <v>73</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
     </row>
-    <row r="31" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C31" s="51" t="s">
         <v>37</v>
       </c>
@@ -2641,7 +2641,7 @@
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
     </row>
-    <row r="32" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C32" s="51" t="s">
         <v>74</v>
       </c>
@@ -2655,7 +2655,7 @@
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
     </row>
-    <row r="33" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C33" s="51" t="s">
         <v>39</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
     </row>
-    <row r="34" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C34" s="38" t="s">
         <v>40</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
     </row>
-    <row r="35" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="51" t="s">
         <v>38</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="K35" s="22"/>
       <c r="L35" s="22"/>
     </row>
-    <row r="36" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="38" t="s">
         <v>77</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="K36" s="22"/>
       <c r="L36" s="22"/>
     </row>
-    <row r="37" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C37" s="38" t="s">
         <v>78</v>
       </c>
@@ -2755,8 +2755,8 @@
       <c r="K37" s="22"/>
       <c r="L37" s="22"/>
     </row>
-    <row r="38" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E39" s="35">
         <f>E28*-1</f>
         <v>5.7095345345345336</v>
@@ -2786,7 +2786,7 @@
         <v>58.647822822822803</v>
       </c>
     </row>
-    <row r="40" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E40" s="35">
         <f>E39/$K$39</f>
         <v>9.7352881312972928E-2</v>
@@ -2813,22 +2813,22 @@
       </c>
       <c r="K40" s="35"/>
     </row>
-    <row r="41" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="71" t="s">
+    <row r="41" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D42" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="71"/>
-      <c r="K42" s="71"/>
-      <c r="L42" s="71"/>
-    </row>
-    <row r="43" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="74" t="s">
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="78"/>
+    </row>
+    <row r="43" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="81" t="s">
         <v>81</v>
       </c>
       <c r="D43" s="51" t="s">
@@ -2859,8 +2859,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="75"/>
+    <row r="44" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="82"/>
       <c r="D44" s="41">
         <v>40</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C45" s="38" t="s">
         <v>72</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C46" s="51" t="s">
         <v>73</v>
       </c>
@@ -2932,7 +2932,7 @@
       <c r="L46" s="22"/>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C47" s="51" t="s">
         <v>37</v>
       </c>
@@ -2947,7 +2947,7 @@
       <c r="L47" s="22"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C48" s="51" t="s">
         <v>74</v>
       </c>
@@ -2962,7 +2962,7 @@
       <c r="L48" s="22"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C49" s="51" t="s">
         <v>39</v>
       </c>
@@ -2977,7 +2977,7 @@
       <c r="L49" s="22"/>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C50" s="38" t="s">
         <v>40</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C51" s="51" t="s">
         <v>38</v>
       </c>
@@ -3012,7 +3012,7 @@
       <c r="L51" s="22"/>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C52" s="38" t="s">
         <v>77</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C53" s="38" t="s">
         <v>78</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D54" s="1"/>
       <c r="E54" s="1">
         <f t="shared" ref="E54:J54" si="13">SUM(E45:E53)</f>
@@ -3086,892 +3086,892 @@
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
     </row>
-    <row r="55" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="3:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="820" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="821" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="822" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="823" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="824" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="825" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="826" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="827" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="828" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="829" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="830" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="831" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="832" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="833" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="834" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="835" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="836" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="837" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="838" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="839" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="840" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="841" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="842" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="843" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="844" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="845" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="846" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="847" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="848" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="849" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="850" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="851" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="852" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="853" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="854" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="855" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="856" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="857" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="858" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="859" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="860" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="861" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="862" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="863" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="864" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="865" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="866" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="867" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="868" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="869" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="870" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="871" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="872" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="873" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="874" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="875" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="876" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="877" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="878" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="879" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="880" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="881" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="882" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="883" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="884" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="885" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="886" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="887" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="888" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="889" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="890" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="891" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="892" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="893" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="894" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="895" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="896" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="897" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="898" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="899" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="900" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="901" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="902" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="903" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="904" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="905" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="906" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="907" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="908" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="909" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="910" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="911" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="912" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="913" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="914" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="915" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="916" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="917" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="918" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="919" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="920" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="921" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="922" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="923" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="924" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="925" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="926" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="927" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="928" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="929" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="930" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="931" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="932" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="933" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="934" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="935" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="936" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="937" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="938" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="939" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="940" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="D42:L42"/>
